--- a/ConverterBoard/bom/ConverterBoard.xlsx
+++ b/ConverterBoard/bom/ConverterBoard.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugod\Documents\ロボット研究部\基板\Robocon2025-PCB\ConverterBoard\bom\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugod\MyFiles\ロボット研究部\基板\Robocon2025-PCB\ConverterBoard\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47EBED2-A8C7-4B7F-A860-B572CDE3BE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABB95D4-8172-4810-9387-4CAD1F2A77F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E87A72D3-F4C2-4E56-AF63-3913EB247CB7}"/>
+    <workbookView xWindow="6210" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{08D47E81-4CAA-49B5-8CB7-498F46F5949F}"/>
   </bookViews>
   <sheets>
     <sheet name="ConverterBoard" sheetId="1" r:id="rId1"/>
+    <sheet name="印刷用" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ConverterBoard!$D$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ConverterBoard!$D$1:$D$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="82">
   <si>
     <t>Reference</t>
   </si>
@@ -74,10 +75,10 @@
     <t>10n</t>
   </si>
   <si>
-    <t>GRM1885C1H103JA01D</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM1885C1H103JA01D/4421555</t>
+    <t>GCM1885C1H103JA16D</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GCM1885C1H103JA16D/13402328</t>
   </si>
   <si>
     <t>C10,C11,C12</t>
@@ -116,6 +117,18 @@
     <t>https://www.digikey.jp/ja/products/detail/diodes-incorporated/B550C-13-F/768772</t>
   </si>
   <si>
+    <t>D4,D5,D6,D7</t>
+  </si>
+  <si>
+    <t>12V,5V,6.5V,BATT</t>
+  </si>
+  <si>
+    <t>SML-D12U8WT86</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/SML-D12U8WT86/1641799</t>
+  </si>
+  <si>
     <t>J1</t>
   </si>
   <si>
@@ -152,7 +165,7 @@
     <t>https://www.digikey.jp/ja/products/detail/taiyo-yuden/NR10050T150M/1171798</t>
   </si>
   <si>
-    <t>L2</t>
+    <t>L2,L3</t>
   </si>
   <si>
     <t>NR10050T220M</t>
@@ -161,18 +174,6 @@
     <t>https://www.digikey.jp/ja/products/detail/taiyo-yuden/NR10050T220M/1007973</t>
   </si>
   <si>
-    <t>L3</t>
-  </si>
-  <si>
-    <t>33u</t>
-  </si>
-  <si>
-    <t>NR10050T330M</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/taiyo-yuden/NR10050T330M/1171799</t>
-  </si>
-  <si>
     <t>R1,R3,R5</t>
   </si>
   <si>
@@ -212,13 +213,52 @@
     <t>R6</t>
   </si>
   <si>
-    <t>11.3k</t>
-  </si>
-  <si>
-    <t>RG1608P-1132-B-T5</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/susumu/RG1608P-1132-B-T5/1240459</t>
+    <t>18k</t>
+  </si>
+  <si>
+    <t>RN73H1JTTD1802B25</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/koa-speer-electronics-inc/RN73H1JTTD1802B25/10688678</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>1.5k</t>
+  </si>
+  <si>
+    <t>ESR03EZPJ152</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPJ152/1983456</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>ESR03EZPJ241</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPJ241/1762728</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>ESR03EZPD3900</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPD3900/21326149</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>ESR03EZPF4990</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPF4990/21819734</t>
   </si>
   <si>
     <t>U1,U2,U3</t>
@@ -251,10 +291,8 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>実質</t>
-    <rPh sb="0" eb="2">
-      <t>ジッシツ</t>
-    </rPh>
+    <t>C13,C14,C15,C16,C17,C18,
+C19,C20,C21,C22,C23,C24</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -855,8 +893,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1232,13 +1270,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C7E483-4884-4EEE-A702-A72D577E2690}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24012796-6F64-4C5B-86BD-C5F31A5F126B}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="4" max="4" width="18.375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -1260,10 +1295,10 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1277,17 +1312,17 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F2">
         <v>6</v>
       </c>
       <c r="G2">
         <f>E2*F2</f>
-        <v>648</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1301,17 +1336,17 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G16" si="0">E3*F3</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <f t="shared" ref="G3:G20" si="0">E3*F3</f>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1335,7 +1370,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1349,17 +1384,17 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>12.9</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>12</v>
       </c>
-      <c r="G5" s="2">
-        <f>E5*F5</f>
-        <v>154.80000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1373,14 +1408,14 @@
         <v>25</v>
       </c>
       <c r="E6">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -1397,17 +1432,17 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1421,14 +1456,14 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
@@ -1445,28 +1480,28 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9">
         <f t="shared" si="0"/>
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>103</v>
@@ -1479,12 +1514,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>43</v>
@@ -1496,14 +1531,14 @@
         <v>103</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -1527,7 +1562,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -1551,7 +1586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -1575,7 +1610,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -1589,17 +1624,17 @@
         <v>60</v>
       </c>
       <c r="E15">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -1613,51 +1648,658 @@
         <v>64</v>
       </c>
       <c r="E16">
-        <v>231</v>
+        <v>22</v>
       </c>
       <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17">
+        <v>240</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17">
+        <v>22</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18">
+        <v>390</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18">
+        <v>31</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19">
+        <v>500</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19">
+        <v>23</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20">
+        <v>241</v>
+      </c>
+      <c r="F20">
         <v>3</v>
       </c>
-      <c r="G16">
-        <f t="shared" si="0"/>
-        <v>693</v>
-      </c>
-    </row>
-    <row r="17" spans="6:8" hidden="1" x14ac:dyDescent="0.4"/>
-    <row r="18" spans="6:8" hidden="1" x14ac:dyDescent="0.4">
-      <c r="F18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="2">
-        <f>SUM(G2:G16)</f>
-        <v>2497.8000000000002</v>
-      </c>
-      <c r="H18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="6:8" hidden="1" x14ac:dyDescent="0.4">
-      <c r="F19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="2">
-        <f>G2+G3+G4+G5+G6+G9+G10+G11+G12+G13+G14+G15+G16</f>
-        <v>2287.8000000000002</v>
-      </c>
-      <c r="H19" t="s">
-        <v>67</v>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>723</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+      <c r="F22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22">
+        <f>SUM(G2:G20)</f>
+        <v>2881</v>
+      </c>
+      <c r="H22" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D19" xr:uid="{19C7E483-4884-4EEE-A702-A72D577E2690}">
+  <autoFilter ref="D1:D22" xr:uid="{24012796-6F64-4C5B-86BD-C5F31A5F126B}">
     <filterColumn colId="0">
       <filters>
-        <filter val="https://akizukidenshi.com/catalog/g/g117950/"/>
-        <filter val="https://akizukidenshi.com/catalog/g/g117953/"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/diodes-incorporated/B550C-13-F/768772"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/koa-speer-electronics-inc/RN73H1JTTD1003B25/10675246"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/koa-speer-electronics-inc/RN73H1JTTD1802B25/10688678"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/koa-speer-electronics-inc/RN73H1JTTD3162B25/10683077"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/koa-speer-electronics-inc/RN73R1JTTD2292B25/10013006"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/murata-electronics/GCJ31CC71E106MA15L/10694168"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/murata-electronics/GCM1885C1H103JA16D/13402328"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/murata-electronics/GCM1885C2A820JA16D/2591816"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/richtek-usa-inc/RT6285GSP/16376754"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPD3900/21326149"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPF4990/21819734"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPJ152/1983456"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/rohm-semiconductor/ESR03EZPJ241/1762728"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/rohm-semiconductor/SML-D12U8WT86/1641799"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/samsung-electro-mechanics/CL31A226KAHNNNE/3888705"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/taiyo-yuden/NR10050T150M/1171798"/>
+        <filter val="https://www.digikey.jp/ja/products/detail/taiyo-yuden/NR10050T220M/1007973"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A127883-FF42-4570-A220-21FECEC9DDE2}">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="23.25" customWidth="1"/>
+    <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="21.125" customWidth="1"/>
+    <col min="5" max="7" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>107</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <f>E2*F2</f>
+        <v>642</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G20" si="0">E3*F3</f>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>15</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>99</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>297</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>60</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10">
+        <v>103</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11">
+        <v>103</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12">
+        <v>15</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13">
+        <v>15</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14">
+        <v>15</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15">
+        <v>32</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16">
+        <v>22</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17">
+        <v>240</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17">
+        <v>22</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18">
+        <v>390</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18">
+        <v>31</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19">
+        <v>500</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19">
+        <v>23</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20">
+        <v>241</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>723</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
+      <c r="F22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22">
+        <f>SUM(G2:G20)</f>
+        <v>2881</v>
+      </c>
+      <c r="H22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>